--- a/StructureDefinition-openimis-communication.xlsx
+++ b/StructureDefinition-openimis-communication.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-26T15:39:34+00:00</t>
+    <t>2025-09-08T11:14:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1501,78 +1501,78 @@
     <t>Communication.payload:DrugReceived.content[x].text</t>
   </si>
   <si>
-    <t>Communication.payload:Asessment</t>
-  </si>
-  <si>
-    <t>Asessment</t>
-  </si>
-  <si>
-    <t>Communication.payload:Asessment.id</t>
-  </si>
-  <si>
-    <t>Communication.payload:Asessment.extension</t>
-  </si>
-  <si>
-    <t>Communication.payload:Asessment.extension:type</t>
-  </si>
-  <si>
-    <t>Communication.payload:Asessment.extension:type.id</t>
-  </si>
-  <si>
-    <t>Communication.payload:Asessment.extension:type.extension</t>
-  </si>
-  <si>
-    <t>Communication.payload:Asessment.extension:type.url</t>
-  </si>
-  <si>
-    <t>Communication.payload:Asessment.extension:type.value[x]</t>
+    <t>Communication.payload:assessment</t>
+  </si>
+  <si>
+    <t>assessment</t>
+  </si>
+  <si>
+    <t>Communication.payload:assessment.id</t>
+  </si>
+  <si>
+    <t>Communication.payload:assessment.extension</t>
+  </si>
+  <si>
+    <t>Communication.payload:assessment.extension:type</t>
+  </si>
+  <si>
+    <t>Communication.payload:assessment.extension:type.id</t>
+  </si>
+  <si>
+    <t>Communication.payload:assessment.extension:type.extension</t>
+  </si>
+  <si>
+    <t>Communication.payload:assessment.extension:type.url</t>
+  </si>
+  <si>
+    <t>Communication.payload:assessment.extension:type.value[x]</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
     &lt;system value="https://github.com/openimis/openimis_fhir_r5_ig/CodeSystem/feedback-payload"/&gt;
-    &lt;code value="Asessment"/&gt;
+    &lt;code value="assessment"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>Communication.payload:Asessment.modifierExtension</t>
-  </si>
-  <si>
-    <t>Communication.payload:Asessment.content[x]</t>
-  </si>
-  <si>
-    <t>Communication.payload:Asessment.content[x].id</t>
-  </si>
-  <si>
-    <t>Communication.payload:Asessment.content[x].extension</t>
-  </si>
-  <si>
-    <t>Communication.payload:Asessment.content[x].coding</t>
-  </si>
-  <si>
-    <t>Communication.payload:Asessment.content[x].coding.id</t>
-  </si>
-  <si>
-    <t>Communication.payload:Asessment.content[x].coding.extension</t>
-  </si>
-  <si>
-    <t>Communication.payload:Asessment.content[x].coding.system</t>
-  </si>
-  <si>
-    <t>Communication.payload:Asessment.content[x].coding.version</t>
-  </si>
-  <si>
-    <t>Communication.payload:Asessment.content[x].coding.code</t>
-  </si>
-  <si>
-    <t>Communication.payload:Asessment.content[x].coding.display</t>
-  </si>
-  <si>
-    <t>Communication.payload:Asessment.content[x].coding.userSelected</t>
-  </si>
-  <si>
-    <t>Communication.payload:Asessment.content[x].text</t>
+    <t>Communication.payload:assessment.modifierExtension</t>
+  </si>
+  <si>
+    <t>Communication.payload:assessment.content[x]</t>
+  </si>
+  <si>
+    <t>Communication.payload:assessment.content[x].id</t>
+  </si>
+  <si>
+    <t>Communication.payload:assessment.content[x].extension</t>
+  </si>
+  <si>
+    <t>Communication.payload:assessment.content[x].coding</t>
+  </si>
+  <si>
+    <t>Communication.payload:assessment.content[x].coding.id</t>
+  </si>
+  <si>
+    <t>Communication.payload:assessment.content[x].coding.extension</t>
+  </si>
+  <si>
+    <t>Communication.payload:assessment.content[x].coding.system</t>
+  </si>
+  <si>
+    <t>Communication.payload:assessment.content[x].coding.version</t>
+  </si>
+  <si>
+    <t>Communication.payload:assessment.content[x].coding.code</t>
+  </si>
+  <si>
+    <t>Communication.payload:assessment.content[x].coding.display</t>
+  </si>
+  <si>
+    <t>Communication.payload:assessment.content[x].coding.userSelected</t>
+  </si>
+  <si>
+    <t>Communication.payload:assessment.content[x].text</t>
   </si>
   <si>
     <t>Communication.note</t>
@@ -3081,7 +3081,7 @@
         <v>78</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>22</v>
@@ -3194,7 +3194,7 @@
         <v>78</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>22</v>
@@ -3303,7 +3303,7 @@
         <v>78</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>22</v>
@@ -3414,7 +3414,7 @@
         <v>78</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>22</v>
@@ -3525,7 +3525,7 @@
         <v>78</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>22</v>
@@ -3636,7 +3636,7 @@
         <v>78</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>22</v>
@@ -3856,7 +3856,7 @@
         <v>78</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>22</v>
@@ -3967,7 +3967,7 @@
         <v>78</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>22</v>
@@ -4078,7 +4078,7 @@
         <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>22</v>
@@ -4191,7 +4191,7 @@
         <v>78</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>22</v>
@@ -4409,7 +4409,7 @@
         <v>78</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>22</v>
@@ -4631,7 +4631,7 @@
         <v>78</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>22</v>
@@ -4742,7 +4742,7 @@
         <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>22</v>
@@ -4851,7 +4851,7 @@
         <v>78</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>22</v>
@@ -4960,7 +4960,7 @@
         <v>78</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>22</v>
@@ -5071,7 +5071,7 @@
         <v>78</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>22</v>
@@ -5180,7 +5180,7 @@
         <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>22</v>
@@ -17564,7 +17564,7 @@
         <v>78</v>
       </c>
       <c r="G142" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H142" t="s" s="2">
         <v>22</v>

--- a/StructureDefinition-openimis-communication.xlsx
+++ b/StructureDefinition-openimis-communication.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-08T11:14:40+00:00</t>
+    <t>2025-09-08T11:37:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-openimis-communication.xlsx
+++ b/StructureDefinition-openimis-communication.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-08T11:37:47+00:00</t>
+    <t>2025-09-08T11:49:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
